--- a/results/job_matches_2026-06-22.xlsx
+++ b/results/job_matches_2026-06-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,24 +591,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, HBase, Spark, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3437af494333f678</t>
+          <t>https://www.indeed.com/viewjob?jk=6b4d18e65e5f0b78</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, HDFS, HBase, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, HBase, Spark, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cb5839d7f1ff18</t>
+          <t>https://www.indeed.com/viewjob?jk=3437af494333f678</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, HDFS, HBase, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a852273f7c50ace</t>
+          <t>https://www.indeed.com/viewjob?jk=54cb5839d7f1ff18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Engineer | Camden Corporate Office</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camden Property Trust</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe0c8f580c4042e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a852273f7c50ace</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Oracle, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da688748068d58e3</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0cbcd1f68bbd17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Oracle, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, Kafka, MySQL, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0cbcd1f68bbd17</t>
+          <t>https://www.indeed.com/viewjob?jk=dad2dad57da48016</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, Kafka, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad2dad57da48016</t>
+          <t>https://www.indeed.com/viewjob?jk=8c56d229b10aedad</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c56d229b10aedad</t>
+          <t>https://www.indeed.com/viewjob?jk=0a30d714c22c8735</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, ETL, Tableau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a30d714c22c8735</t>
+          <t>https://www.indeed.com/viewjob?jk=668fd578e5ad205b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, ETL, Tableau</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668fd578e5ad205b</t>
+          <t>https://www.indeed.com/viewjob?jk=1eaf063221a10b37</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eaf063221a10b37</t>
+          <t>https://www.indeed.com/viewjob?jk=0ce59f430b705383</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,15 +1283,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ce59f430b705383</t>
+          <t>https://www.indeed.com/viewjob?jk=afe0d6afd5890323</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe0d6afd5890323</t>
+          <t>https://www.indeed.com/viewjob?jk=ce50156e09e284be</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce50156e09e284be</t>
+          <t>https://www.indeed.com/viewjob?jk=6205d2f26b1a8bd9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6205d2f26b1a8bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=da39ecae1ec3ea0f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da39ecae1ec3ea0f</t>
+          <t>https://www.indeed.com/viewjob?jk=24ae1753ad2a27d5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,15 +1458,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ae1753ad2a27d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e96a792ded5789cd</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96a792ded5789cd</t>
+          <t>https://www.indeed.com/viewjob?jk=53032a4f73d83e5c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53032a4f73d83e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f4919174f0cd9fd1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4919174f0cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=562e8a2839504d14</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562e8a2839504d14</t>
+          <t>https://www.indeed.com/viewjob?jk=a64bab937e1605b3</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64bab937e1605b3</t>
+          <t>https://www.indeed.com/viewjob?jk=c8efbd88a354542d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Kafka, MySQL</t>
+          <t>AWS, RDS, HBase, Spark, Kafka, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8efbd88a354542d</t>
+          <t>https://www.indeed.com/viewjob?jk=5e185b13ff1bfe4c</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Kafka, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e185b13ff1bfe4c</t>
+          <t>https://www.indeed.com/viewjob?jk=1479a392d9628a14</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,15 +1738,15 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1479a392d9628a14</t>
+          <t>https://www.indeed.com/viewjob?jk=5b570e647466948e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, ETL, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b570e647466948e</t>
+          <t>https://www.indeed.com/viewjob?jk=83344ad97f6d0723</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, ETL, Tableau</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83344ad97f6d0723</t>
+          <t>https://www.indeed.com/viewjob?jk=ed47cf62aeed008b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,24 +1851,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed47cf62aeed008b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d6f5314015483d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Sr Security Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d6f5314015483d</t>
+          <t>https://www.indeed.com/viewjob?jk=975ac3cab8fe8b4d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, ETL, Tableau, Python</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975ac3cab8fe8b4d</t>
+          <t>https://www.indeed.com/viewjob?jk=684ac425090f80d4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1952,11 +1952,11 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, ETL, Tableau, Python</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Oracle, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684ac425090f80d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5f36b69a2642649b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Oracle, Tableau, Git, Python, SQL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MySQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f36b69a2642649b</t>
+          <t>https://www.indeed.com/viewjob?jk=576587c3beb8fa6e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MySQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Scala, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576587c3beb8fa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8e2f411bfd2f2d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Scala, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8e2f411bfd2f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=8cb58a77c3b1339a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,24 +2096,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cb58a77c3b1339a</t>
+          <t>https://www.indeed.com/viewjob?jk=b786d28f512935cf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, NoSQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50166ea86bb9965</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b71213ece018bb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b786d28f512935cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c50166ea86bb9965</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, NoSQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Hadoop, HDFS, ETL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b71213ece018bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9e43322fd80b5294</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, ETL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e43322fd80b5294</t>
+          <t>https://www.indeed.com/viewjob?jk=edf61855d4ab5e16</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf61855d4ab5e16</t>
+          <t>https://www.indeed.com/viewjob?jk=32f351a5adb8088f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Hive, MySQL, Cassandra, NoSQL, Data Modeling, Tableau, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2315,41 +2315,6 @@
         </is>
       </c>
       <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32f351a5adb8088f</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hive, MySQL, Cassandra, NoSQL, Data Modeling, Tableau, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3b38ea20568618d5</t>
         </is>

--- a/results/job_matches_2026-06-22.xlsx
+++ b/results/job_matches_2026-06-22.xlsx
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SENIOR PYTHON DEVELOPER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,24 +1431,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ae1753ad2a27d5</t>
+          <t>https://www.indeed.com/viewjob?jk=25e80cbc986d4ce6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,15 +1458,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96a792ded5789cd</t>
+          <t>https://www.indeed.com/viewjob?jk=24ae1753ad2a27d5</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53032a4f73d83e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=e96a792ded5789cd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4919174f0cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=53032a4f73d83e5c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, MySQL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562e8a2839504d14</t>
+          <t>https://www.indeed.com/viewjob?jk=f4919174f0cd9fd1</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64bab937e1605b3</t>
+          <t>https://www.indeed.com/viewjob?jk=562e8a2839504d14</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8efbd88a354542d</t>
+          <t>https://www.indeed.com/viewjob?jk=a64bab937e1605b3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Kafka, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e185b13ff1bfe4c</t>
+          <t>https://www.indeed.com/viewjob?jk=c8efbd88a354542d</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, HBase, Spark, Kafka, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1479a392d9628a14</t>
+          <t>https://www.indeed.com/viewjob?jk=5e185b13ff1bfe4c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,15 +1738,15 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b570e647466948e</t>
+          <t>https://www.indeed.com/viewjob?jk=1479a392d9628a14</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83344ad97f6d0723</t>
+          <t>https://www.indeed.com/viewjob?jk=5b570e647466948e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, ETL, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed47cf62aeed008b</t>
+          <t>https://www.indeed.com/viewjob?jk=83344ad97f6d0723</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b786d28f512935cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c50166ea86bb9965</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, NoSQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b71213ece018bb</t>
+          <t>https://www.indeed.com/viewjob?jk=b786d28f512935cf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, NoSQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50166ea86bb9965</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b71213ece018bb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-22.xlsx
+++ b/results/job_matches_2026-06-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aldie, VA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0215398446cd7f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=87befe694c7b985a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,11 +513,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87befe694c7b985a</t>
+          <t>https://www.indeed.com/viewjob?jk=be71c50bf15a0668</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, HBase, Spark</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be71c50bf15a0668</t>
+          <t>https://www.indeed.com/viewjob?jk=2fe3e1ce3f976c6b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, EMR, Redshift, S3, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b4d18e65e5f0b78</t>
+          <t>https://www.indeed.com/viewjob?jk=1489cddaebca9c0c</t>
         </is>
       </c>
     </row>
@@ -1028,112 +1028,112 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Oracle, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0cbcd1f68bbd17</t>
+          <t>https://www.indeed.com/viewjob?jk=513e4c068f57c27c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, Kafka, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad2dad57da48016</t>
+          <t>https://www.indeed.com/viewjob?jk=8e317b647d670c88</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer Associate - Full Stack (ETF Focused)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c56d229b10aedad</t>
+          <t>https://www.indeed.com/viewjob?jk=af2f21ad2271e214</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a30d714c22c8735</t>
+          <t>https://www.indeed.com/viewjob?jk=8c56d229b10aedad</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,15 +1178,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Oracle, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668fd578e5ad205b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0cbcd1f68bbd17</t>
         </is>
       </c>
     </row>
@@ -1213,15 +1213,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, MLOps</t>
+          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, Kafka, MySQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eaf063221a10b37</t>
+          <t>https://www.indeed.com/viewjob?jk=dad2dad57da48016</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Agentic AI Engineer II - Cyber Analytics</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,24 +1256,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ce59f430b705383</t>
+          <t>https://www.indeed.com/viewjob?jk=705011c4830be681</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe0d6afd5890323</t>
+          <t>https://www.indeed.com/viewjob?jk=0a30d714c22c8735</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, ETL, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce50156e09e284be</t>
+          <t>https://www.indeed.com/viewjob?jk=668fd578e5ad205b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,15 +1353,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6205d2f26b1a8bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=1eaf063221a10b37</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,11 +1388,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da39ecae1ec3ea0f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ce59f430b705383</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SENIOR PYTHON DEVELOPER</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Gray Operations Group, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Aberdeen, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,112 +1441,112 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e80cbc986d4ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=3dac14b064b52504</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>COTOC LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Oracle, ETL</t>
+          <t>AWS, S3, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ae1753ad2a27d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b0a9b3e3d1d545</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer Associate - Full Stack</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96a792ded5789cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab09e0090bf42cf7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Cloud Engineer - Storage Specialist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53032a4f73d83e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5184de3aab6b232</t>
         </is>
       </c>
     </row>
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4919174f0cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=afe0d6afd5890323</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,15 +1598,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562e8a2839504d14</t>
+          <t>https://www.indeed.com/viewjob?jk=ce50156e09e284be</t>
         </is>
       </c>
     </row>
@@ -1633,15 +1633,15 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64bab937e1605b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6205d2f26b1a8bd9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,15 +1668,15 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,84 +1686,84 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8efbd88a354542d</t>
+          <t>https://www.indeed.com/viewjob?jk=da39ecae1ec3ea0f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>SENIOR PYTHON DEVELOPER</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Kafka, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e185b13ff1bfe4c</t>
+          <t>https://www.indeed.com/viewjob?jk=25e80cbc986d4ce6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Website Developer (4+ Yrs.)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Bluestage</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1479a392d9628a14</t>
+          <t>https://www.indeed.com/viewjob?jk=76195dce425feed6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1773,15 +1773,15 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b570e647466948e</t>
+          <t>https://www.indeed.com/viewjob?jk=24ae1753ad2a27d5</t>
         </is>
       </c>
     </row>
@@ -1808,15 +1808,15 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83344ad97f6d0723</t>
+          <t>https://www.indeed.com/viewjob?jk=e96a792ded5789cd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,15 +1843,15 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,49 +1861,49 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d6f5314015483d</t>
+          <t>https://www.indeed.com/viewjob?jk=53032a4f73d83e5c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Seurat Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, Photon, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975ac3cab8fe8b4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, ETL, Tableau, Python</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684ac425090f80d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f4919174f0cd9fd1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,15 +1948,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Oracle, Tableau, Git, Python, SQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f36b69a2642649b</t>
+          <t>https://www.indeed.com/viewjob?jk=562e8a2839504d14</t>
         </is>
       </c>
     </row>
@@ -1983,15 +1983,15 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MySQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576587c3beb8fa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=a64bab937e1605b3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2022,11 +2022,11 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Scala, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,49 +2036,49 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8e2f411bfd2f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8efbd88a354542d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cb58a77c3b1339a</t>
+          <t>https://www.indeed.com/viewjob?jk=1479a392d9628a14</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,15 +2088,15 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, HBase, Spark, Kafka, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50166ea86bb9965</t>
+          <t>https://www.indeed.com/viewjob?jk=5e185b13ff1bfe4c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,15 +2123,15 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,49 +2141,49 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b786d28f512935cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5b570e647466948e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, NoSQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Dataflow, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b71213ece018bb</t>
+          <t>https://www.indeed.com/viewjob?jk=d897690a96d924bc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2197,11 +2197,11 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, ETL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, ETL, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e43322fd80b5294</t>
+          <t>https://www.indeed.com/viewjob?jk=83344ad97f6d0723</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf61855d4ab5e16</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d6f5314015483d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Sr Security Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,15 +2263,15 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f351a5adb8088f</t>
+          <t>https://www.indeed.com/viewjob?jk=975ac3cab8fe8b4d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,25 +2298,655 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, ETL, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=684ac425090f80d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c328c7448124caa</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D56" t="n">
         <v>10.4</v>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hive, MySQL, Cassandra, NoSQL, Data Modeling, Tableau, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b38ea20568618d5</t>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03a2f833ade47dc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a05c65027f02540</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cea857b2446e2cf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f98a7522f331ea86</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55fa1a739f4dfcad</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Oracle, Tableau, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f36b69a2642649b</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MySQL, ETL, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=576587c3beb8fa6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Scala, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c8e2f411bfd2f2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Azure Data Engineer - State National</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Markel Corporation</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Bedford, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cb58a77c3b1339a</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Sr. Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, ETL</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c50166ea86bb9965</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b786d28f512935cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, MySQL, NoSQL, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5b71213ece018bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HDFS, ETL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e43322fd80b5294</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, ETL, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edf61855d4ab5e16</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32f351a5adb8088f</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer I - Java - Ace Studio Platform</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, HBase, Spark, Kafka, Cassandra, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61154a8efcdc6de3</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Information Protection Senior Advisor - (Cloud Vulnerability Management)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Bloomington, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59fa7e96028f2f89</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-22.xlsx
+++ b/results/job_matches_2026-06-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, HBase, Spark</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87befe694c7b985a</t>
+          <t>https://www.indeed.com/viewjob?jk=2fe3e1ce3f976c6b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, HBase, Spark</t>
+          <t>AWS, EMR, Redshift, S3, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be71c50bf15a0668</t>
+          <t>https://www.indeed.com/viewjob?jk=1489cddaebca9c0c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fe3e1ce3f976c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=8e317b647d670c88</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Database Engineer</t>
+          <t>Software Engineer Associate - Full Stack (ETF Focused)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,452 +601,452 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1489cddaebca9c0c</t>
+          <t>https://www.indeed.com/viewjob?jk=af2f21ad2271e214</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Skillable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, HBase, Spark, Kafka</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3437af494333f678</t>
+          <t>https://www.indeed.com/viewjob?jk=311fae6e7852845c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Agentic AI Engineer II - Cyber Analytics</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, HDFS, HBase, Spark</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cb5839d7f1ff18</t>
+          <t>https://www.indeed.com/viewjob?jk=705011c4830be681</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a852273f7c50ace</t>
+          <t>https://www.indeed.com/viewjob?jk=901037a80c58288a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, HBase, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b23c16e9f7fa792e</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf9fb3151d6e1d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, HBase, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac9dc3219cfc4a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ee45bf9eb0ffba</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2266c4dba2263dcf</t>
+          <t>https://www.indeed.com/viewjob?jk=d55836148ef2a5d2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, HBase, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c005a7e163f3e45</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e4e7d744b937a4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2138ac157376b704</t>
+          <t>https://www.indeed.com/viewjob?jk=6a97de4c50830683</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330a92d6908ce8a5</t>
+          <t>https://www.indeed.com/viewjob?jk=6adcbc9e8685b739</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Gray Operations Group, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Aberdeen, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Hadoop, HDFS, Scala, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=957be306b670cbe5</t>
+          <t>https://www.indeed.com/viewjob?jk=3dac14b064b52504</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>COTOC LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113b681733f9747f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b0a9b3e3d1d545</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Engineer - Supply Chain</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, HBase, Spark, PySpark</t>
+          <t>RDS, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=258440f6c426d01d</t>
+          <t>https://www.indeed.com/viewjob?jk=c337227860ec1abc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>AWS Cloud Engineer - Storage Specialist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=513e4c068f57c27c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5184de3aab6b232</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>SENIOR PYTHON DEVELOPER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e317b647d670c88</t>
+          <t>https://www.indeed.com/viewjob?jk=25e80cbc986d4ce6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer Associate - Full Stack (ETF Focused)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,137 +1126,137 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af2f21ad2271e214</t>
+          <t>https://www.indeed.com/viewjob?jk=da7ab691a0b00d67</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c56d229b10aedad</t>
+          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Seurat Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Oracle, MySQL, Cassandra, NoSQL</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, Photon, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0cbcd1f68bbd17</t>
+          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Performance Database Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, Kafka, MySQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad2dad57da48016</t>
+          <t>https://www.indeed.com/viewjob?jk=e4925c6e7012876a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer II - Cyber Analytics</t>
+          <t>Application Architect (contract)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,172 +1266,172 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705011c4830be681</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4005e09738f87b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Systems Integration Engineer 3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>UC San Diego</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kafka, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a30d714c22c8735</t>
+          <t>https://www.indeed.com/viewjob?jk=656b4089fd66ca54</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, ETL, Tableau</t>
+          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668fd578e5ad205b</t>
+          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Data Engineer- Integrations</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Health Catalyst</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, MLOps</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eaf063221a10b37</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6de5fb7f1d0546</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Acima Leasing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ce59f430b705383</t>
+          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Data Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gray Operations Group, Inc.</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Aberdeen, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, dbt, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dac14b064b52504</t>
+          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>COTOC LLC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Dataflow, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b0a9b3e3d1d545</t>
+          <t>https://www.indeed.com/viewjob?jk=d897690a96d924bc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer Associate - Full Stack</t>
+          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab09e0090bf42cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=394b99227e255a87</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - Storage Specialist</t>
+          <t>Consultant, Strategy and Business Analytics</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, SQL Server, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,172 +1546,172 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5184de3aab6b232</t>
+          <t>https://www.indeed.com/viewjob?jk=34a7ab2b3bfa1663</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe0d6afd5890323</t>
+          <t>https://www.indeed.com/viewjob?jk=1105ec475da982ae</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce50156e09e284be</t>
+          <t>https://www.indeed.com/viewjob?jk=5604c52f06d0ee25</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6205d2f26b1a8bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=66c9d330852f409d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da39ecae1ec3ea0f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a3081bc81bfba1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SENIOR PYTHON DEVELOPER</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e80cbc986d4ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=ded0c7a9dceb7dc8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Website Developer (4+ Yrs.)</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bluestage</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,137 +1756,137 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76195dce425feed6</t>
+          <t>https://www.indeed.com/viewjob?jk=860741b7d7b95265</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ae1753ad2a27d5</t>
+          <t>https://www.indeed.com/viewjob?jk=b223dc2b5127ecf4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96a792ded5789cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9420fc6b40ef2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53032a4f73d83e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=eefa74af3d61ebf7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Seurat Technologies</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, Photon, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,42 +1896,42 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
+          <t>https://www.indeed.com/viewjob?jk=724915d9ab75c4bc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4919174f0cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c328c7448124caa</t>
         </is>
       </c>
     </row>
@@ -1943,30 +1943,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562e8a2839504d14</t>
+          <t>https://www.indeed.com/viewjob?jk=03a2f833ade47dc6</t>
         </is>
       </c>
     </row>
@@ -1978,30 +1978,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64bab937e1605b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6a05c65027f02540</t>
         </is>
       </c>
     </row>
@@ -2013,160 +2013,160 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8efbd88a354542d</t>
+          <t>https://www.indeed.com/viewjob?jk=cea857b2446e2cf4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1479a392d9628a14</t>
+          <t>https://www.indeed.com/viewjob?jk=f98a7522f331ea86</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Kafka, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e185b13ff1bfe4c</t>
+          <t>https://www.indeed.com/viewjob?jk=55fa1a739f4dfcad</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b570e647466948e</t>
+          <t>https://www.indeed.com/viewjob?jk=8c9d974e64a10e28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>System Architect – Platform Engineering</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,777 +2176,147 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d897690a96d924bc</t>
+          <t>https://www.indeed.com/viewjob?jk=f81a3257ca39d82e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, ETL, Tableau</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83344ad97f6d0723</t>
+          <t>https://www.indeed.com/viewjob?jk=619827434d7e7a20</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d6f5314015483d</t>
+          <t>https://www.indeed.com/viewjob?jk=dea59b60f49359e2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Security Engineer</t>
+          <t>Sr Software Engineer I - Java - Ace Studio Platform</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, HBase, Spark, Kafka, Cassandra, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975ac3cab8fe8b4d</t>
+          <t>https://www.indeed.com/viewjob?jk=61154a8efcdc6de3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, ETL, Tableau, Python</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684ac425090f80d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>PrizePicks</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c328c7448124caa</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>PrizePicks</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03a2f833ade47dc6</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>PrizePicks</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a05c65027f02540</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>PrizePicks</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cea857b2446e2cf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>PrizePicks</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f98a7522f331ea86</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>PrizePicks</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55fa1a739f4dfcad</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Sr Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>RI, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Oracle, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f36b69a2642649b</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>RI, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MySQL, ETL, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=576587c3beb8fa6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Scala, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8e2f411bfd2f2d</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Azure Data Engineer - State National</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Markel Corporation</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Bedford, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8cb58a77c3b1339a</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Sr. Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, ETL</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c50166ea86bb9965</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>MA, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b786d28f512935cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, NoSQL, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b71213ece018bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, HDFS, ETL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e43322fd80b5294</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Sr. Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>RI, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, ETL, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edf61855d4ab5e16</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Sr Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32f351a5adb8088f</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer I - Java - Ace Studio Platform</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, HBase, Spark, Kafka, Cassandra, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61154a8efcdc6de3</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Information Protection Senior Advisor - (Cloud Vulnerability Management)</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>The Cigna Group</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Bloomington, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=59fa7e96028f2f89</t>
+          <t>https://www.indeed.com/viewjob?jk=12abd2998788b1bc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-22.xlsx
+++ b/results/job_matches_2026-06-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>AI/ML Engineer - Houston Only</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>FuGen IT Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Brownsville, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>RDS, Hadoop, HDFS, Hive, Sqoop, HBase, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e317b647d670c88</t>
+          <t>https://www.indeed.com/viewjob?jk=65948e9315786e1b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer Associate - Full Stack (ETF Focused)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>FuGen IT Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Hadoop, HDFS, Hive, Sqoop, HBase, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af2f21ad2271e214</t>
+          <t>https://www.indeed.com/viewjob?jk=6be023b7abd58b5c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Scientist/ Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Skillable</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311fae6e7852845c</t>
+          <t>https://www.indeed.com/viewjob?jk=17be7a125f62a198</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer II - Cyber Analytics</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705011c4830be681</t>
+          <t>https://www.indeed.com/viewjob?jk=8e317b647d670c88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer Associate - Full Stack (ETF Focused)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901037a80c58288a</t>
+          <t>https://www.indeed.com/viewjob?jk=af2f21ad2271e214</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Skillable</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf9fb3151d6e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=311fae6e7852845c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Agentic AI Engineer II - Cyber Analytics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ee45bf9eb0ffba</t>
+          <t>https://www.indeed.com/viewjob?jk=705011c4830be681</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55836148ef2a5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=901037a80c58288a</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e4e7d744b937a4</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf9fb3151d6e1d</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a97de4c50830683</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ee45bf9eb0ffba</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adcbc9e8685b739</t>
+          <t>https://www.indeed.com/viewjob?jk=d55836148ef2a5d2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gray Operations Group, Inc.</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aberdeen, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dac14b064b52504</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e4e7d744b937a4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COTOC LLC</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b0a9b3e3d1d545</t>
+          <t>https://www.indeed.com/viewjob?jk=6a97de4c50830683</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Supply Chain</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c337227860ec1abc</t>
+          <t>https://www.indeed.com/viewjob?jk=6adcbc9e8685b739</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - Storage Specialist</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Gray Operations Group, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Aberdeen, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5184de3aab6b232</t>
+          <t>https://www.indeed.com/viewjob?jk=3dac14b064b52504</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SENIOR PYTHON DEVELOPER</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>COTOC LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e80cbc986d4ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b0a9b3e3d1d545</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Engineer - Supply Chain</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>RDS, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7ab691a0b00d67</t>
+          <t>https://www.indeed.com/viewjob?jk=c337227860ec1abc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Engineer - Storage Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
+          <t>https://www.indeed.com/viewjob?jk=b5184de3aab6b232</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Seurat Technologies</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, Photon, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, ETL, REST API integration, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Performance Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4925c6e7012876a</t>
+          <t>https://www.indeed.com/viewjob?jk=da7ab691a0b00d67</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Application Architect (contract)</t>
+          <t>SENIOR PYTHON DEVELOPER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4005e09738f87b</t>
+          <t>https://www.indeed.com/viewjob?jk=25e80cbc986d4ce6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Systems Integration Engineer 3</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UC San Diego</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kafka, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656b4089fd66ca54</t>
+          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Seurat Technologies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, Photon, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
+          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Engineer- Integrations</t>
+          <t>Data Architect – Sales &amp; Marketing Technology</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Health Catalyst</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6de5fb7f1d0546</t>
+          <t>https://www.indeed.com/viewjob?jk=90f73e409f24d7f3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Acima Leasing</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
+          <t>https://www.indeed.com/viewjob?jk=c96ebe8f7e65bd71</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer II</t>
+          <t>Senior Performance Database Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, dbt, Kubernetes, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e4925c6e7012876a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Application Architect (contract)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d897690a96d924bc</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4005e09738f87b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
+          <t>Systems Integration Engineer 3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>UC San Diego</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kafka, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394b99227e255a87</t>
+          <t>https://www.indeed.com/viewjob?jk=656b4089fd66ca54</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Consultant, Strategy and Business Analytics</t>
+          <t>Sr Data Engineer- Integrations</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Health Catalyst</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, SQL Server, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7ab2b3bfa1663</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6de5fb7f1d0546</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Acima Leasing</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1105ec475da982ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Senior Data Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, dbt, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5604c52f06d0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Dataflow, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c9d330852f409d</t>
+          <t>https://www.indeed.com/viewjob?jk=d897690a96d924bc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>FuGen IT Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a3081bc81bfba1</t>
+          <t>https://www.indeed.com/viewjob?jk=356a0ca018ded67d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded0c7a9dceb7dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,54 +1756,54 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860741b7d7b95265</t>
+          <t>https://www.indeed.com/viewjob?jk=394b99227e255a87</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b223dc2b5127ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=1105ec475da982ae</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9420fc6b40ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=8c328c7448124caa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,19 +1861,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eefa74af3d61ebf7</t>
+          <t>https://www.indeed.com/viewjob?jk=03a2f833ade47dc6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724915d9ab75c4bc</t>
+          <t>https://www.indeed.com/viewjob?jk=6a05c65027f02540</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c328c7448124caa</t>
+          <t>https://www.indeed.com/viewjob?jk=cea857b2446e2cf4</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a2f833ade47dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=f98a7522f331ea86</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a05c65027f02540</t>
+          <t>https://www.indeed.com/viewjob?jk=55fa1a739f4dfcad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,19 +2036,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea857b2446e2cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=5604c52f06d0ee25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f98a7522f331ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=66c9d330852f409d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fa1a739f4dfcad</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a3081bc81bfba1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>UX Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c9d974e64a10e28</t>
+          <t>https://www.indeed.com/viewjob?jk=ded0c7a9dceb7dc8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>System Architect – Platform Engineering</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,19 +2176,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f81a3257ca39d82e</t>
+          <t>https://www.indeed.com/viewjob?jk=860741b7d7b95265</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619827434d7e7a20</t>
+          <t>https://www.indeed.com/viewjob?jk=b223dc2b5127ecf4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea59b60f49359e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9420fc6b40ef2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Java - Ace Studio Platform</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Kafka, Cassandra, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61154a8efcdc6de3</t>
+          <t>https://www.indeed.com/viewjob?jk=eefa74af3d61ebf7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,297 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=724915d9ab75c4bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>UX Software Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Charles River Analytics</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c9d974e64a10e28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Information Protection Senior Advisor - (Cloud Vulnerability Management)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Bloomington, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36165d879b274964</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Southern New Hampshire University</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, GCP, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=12abd2998788b1bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>System Architect – Platform Engineering</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f81a3257ca39d82e</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=619827434d7e7a20</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dea59b60f49359e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Citian</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b974af9691c4f73</t>
         </is>
       </c>
     </row>
